--- a/exports/trend_1d/NIFTYNXT50_full_report.xlsx
+++ b/exports/trend_1d/NIFTYNXT50_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.43</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>19081.59</v>
+        <v>18742.34</v>
       </c>
       <c r="I2" t="n">
         <v>18979.90714350061</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>0.82</v>
+        <v>-0.97</v>
       </c>
       <c r="L2" t="n">
-        <v>0.48</v>
+        <v>1.15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08</v>
+        <v>0.73</v>
       </c>
       <c r="N2" t="n">
-        <v>1.12</v>
+        <v>1.78</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>4.95</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42054</v>
+        <v>42055</v>
       </c>
       <c r="H3" t="n">
-        <v>19645.3</v>
+        <v>19696.4</v>
       </c>
       <c r="I3" t="n">
         <v>19670.84687523081</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.82</v>
+        <v>-5.09</v>
       </c>
       <c r="L3" t="n">
         <v>5.6</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>4.3</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H4" t="n">
-        <v>19344.05</v>
+        <v>19112.05</v>
       </c>
       <c r="I4" t="n">
         <v>19174.62028344165</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.79</v>
+        <v>-2.97</v>
       </c>
       <c r="L4" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="M4" t="n">
         <v>0.38</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>4.69</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42100</v>
+        <v>42101</v>
       </c>
       <c r="H5" t="n">
-        <v>19819.75</v>
+        <v>20027.75</v>
       </c>
       <c r="I5" t="n">
         <v>19878.90104680322</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.7</v>
+        <v>-4.79</v>
       </c>
       <c r="L5" t="n">
-        <v>3.86</v>
+        <v>4.96</v>
       </c>
       <c r="M5" t="n">
         <v>0.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>4.84</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H6" t="n">
-        <v>19898.9</v>
+        <v>19500.05</v>
       </c>
       <c r="I6" t="n">
         <v>19671.86575762487</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.64</v>
+        <v>-2.63</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>3.36</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>1.05</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>5.64</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H7" t="n">
-        <v>19696.25</v>
+        <v>19930.3</v>
       </c>
       <c r="I7" t="n">
         <v>19823.17821231693</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.01</v>
+        <v>-2.21</v>
       </c>
       <c r="L7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="M7" t="n">
         <v>0.74</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42160</v>
+        <v>42163</v>
       </c>
       <c r="H8" t="n">
-        <v>19243.84</v>
+        <v>18983.95</v>
       </c>
       <c r="I8" t="n">
         <v>19071.12878344058</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.44</v>
+        <v>-4.75</v>
       </c>
       <c r="L8" t="n">
         <v>5.58</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.69</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42174</v>
+        <v>42177</v>
       </c>
       <c r="H9" t="n">
-        <v>19524.59</v>
+        <v>19819.8</v>
       </c>
       <c r="I9" t="n">
         <v>19724.29425613344</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.85</v>
+        <v>-4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
         <v>0.65</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.8</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H10" t="n">
-        <v>20877.2</v>
+        <v>20806.55</v>
       </c>
       <c r="I10" t="n">
         <v>20866.70983890291</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K10" t="n">
-        <v>5.34</v>
+        <v>4.98</v>
       </c>
       <c r="L10" t="n">
         <v>2.6</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42356</v>
+        <v>42359</v>
       </c>
       <c r="H11" t="n">
-        <v>19593.84</v>
+        <v>19724.75</v>
       </c>
       <c r="I11" t="n">
         <v>19675.05176527231</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K11" t="n">
-        <v>5.83</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>3.9</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>3.45</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H12" t="n">
-        <v>20008.7</v>
+        <v>19408.15</v>
       </c>
       <c r="I12" t="n">
         <v>19570.58075624577</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>1.44</v>
+        <v>-1.61</v>
       </c>
       <c r="L12" t="n">
-        <v>0.71</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
       <c r="N12" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0.67</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.65</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H13" t="n">
-        <v>17901.55</v>
+        <v>18030.8</v>
       </c>
       <c r="I13" t="n">
         <v>17992.92259378619</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K13" t="n">
-        <v>7.76</v>
+        <v>7.1</v>
       </c>
       <c r="L13" t="n">
         <v>2.24</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.07</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H14" t="n">
-        <v>23339.1</v>
+        <v>22674.6</v>
       </c>
       <c r="I14" t="n">
         <v>22854.60608522903</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K14" t="n">
-        <v>29.44</v>
+        <v>25.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.1</v>
@@ -1239,7 +1406,7 @@
         <v>2.23</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
         <v>0.72</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>4.23</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42647</v>
+        <v>42648</v>
       </c>
       <c r="H15" t="n">
-        <v>23684.25</v>
+        <v>23722.25</v>
       </c>
       <c r="I15" t="n">
         <v>23699.47457049728</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.45</v>
+        <v>-4.62</v>
       </c>
       <c r="L15" t="n">
-        <v>4.64</v>
+        <v>4.89</v>
       </c>
       <c r="M15" t="n">
         <v>0.9399999999999999</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.45</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H16" t="n">
-        <v>22910.8</v>
+        <v>22621.55</v>
       </c>
       <c r="I16" t="n">
         <v>22900.63328115299</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.42</v>
+        <v>-4.64</v>
       </c>
       <c r="L16" t="n">
-        <v>3.63</v>
+        <v>5.67</v>
       </c>
       <c r="M16" t="n">
         <v>0.9</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.71</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H17" t="n">
-        <v>21389.7</v>
+        <v>21580.25</v>
       </c>
       <c r="I17" t="n">
         <v>21488.93415686575</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
-        <v>5.45</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>2.07</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.77</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H18" t="n">
-        <v>26251.05</v>
+        <v>26099.3</v>
       </c>
       <c r="I18" t="n">
         <v>26200.12938925721</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K18" t="n">
-        <v>21.64</v>
+        <v>20.94</v>
       </c>
       <c r="L18" t="n">
         <v>1.08</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>3.92</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42893</v>
+        <v>42894</v>
       </c>
       <c r="H19" t="n">
-        <v>26422.6</v>
+        <v>26507.25</v>
       </c>
       <c r="I19" t="n">
         <v>26478.46668832938</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.24</v>
+        <v>-1.56</v>
       </c>
       <c r="L19" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
         <v>0.7</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>3.62</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42909</v>
+        <v>42913</v>
       </c>
       <c r="H20" t="n">
-        <v>26157.9</v>
+        <v>25968.2</v>
       </c>
       <c r="I20" t="n">
         <v>25973.35187898942</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.32</v>
+        <v>-2.03</v>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2.76</v>
       </c>
       <c r="M20" t="n">
         <v>0.04</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>3.5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42921</v>
+        <v>42922</v>
       </c>
       <c r="H21" t="n">
-        <v>26756.05</v>
+        <v>26869.65</v>
       </c>
       <c r="I21" t="n">
         <v>26810.61219469505</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.03</v>
+        <v>-3.47</v>
       </c>
       <c r="L21" t="n">
-        <v>3.15</v>
+        <v>3.77</v>
       </c>
       <c r="M21" t="n">
         <v>0.35</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>3.05</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H22" t="n">
-        <v>27652</v>
+        <v>26895.05</v>
       </c>
       <c r="I22" t="n">
         <v>27479.71208895248</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>2.91</v>
+        <v>0.09</v>
       </c>
       <c r="L22" t="n">
-        <v>0.35</v>
+        <v>1.08</v>
       </c>
       <c r="M22" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
         <v>0.42</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.35</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H23" t="n">
-        <v>28054.4</v>
+        <v>28338.35</v>
       </c>
       <c r="I23" t="n">
         <v>28144.30002843828</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.31</v>
+        <v>-5.37</v>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>5.49</v>
       </c>
       <c r="M23" t="n">
         <v>0.82</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H24" t="n">
-        <v>28695.45</v>
+        <v>27947.25</v>
       </c>
       <c r="I24" t="n">
         <v>28056.37491303744</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>1.26</v>
+        <v>-1.38</v>
       </c>
       <c r="L24" t="n">
         <v>1.63</v>
@@ -1809,7 +2096,7 @@
         <v>0.51</v>
       </c>
       <c r="N24" t="n">
-        <v>0.72</v>
+        <v>2.61</v>
       </c>
       <c r="O24" t="n">
         <v>1.01</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43019</v>
+        <v>43020</v>
       </c>
       <c r="H25" t="n">
-        <v>28214.85</v>
+        <v>28528.85</v>
       </c>
       <c r="I25" t="n">
         <v>28412.56139589047</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.96</v>
+        <v>-2.08</v>
       </c>
       <c r="L25" t="n">
         <v>2.36</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>4.47</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H26" t="n">
-        <v>29353.6</v>
+        <v>29014.75</v>
       </c>
       <c r="I26" t="n">
         <v>29347.39997230453</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>2.89</v>
+        <v>1.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.27</v>
       </c>
       <c r="M26" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="N26" t="n">
         <v>1.53</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.07</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43087</v>
+        <v>43088</v>
       </c>
       <c r="H27" t="n">
-        <v>30042.25</v>
+        <v>30473.4</v>
       </c>
       <c r="I27" t="n">
         <v>30194.93860197915</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.54</v>
+        <v>-5.03</v>
       </c>
       <c r="L27" t="n">
-        <v>4.02</v>
+        <v>5.1</v>
       </c>
       <c r="M27" t="n">
         <v>1.16</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.75</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H28" t="n">
-        <v>30891.2</v>
+        <v>30712.4</v>
       </c>
       <c r="I28" t="n">
         <v>30823.2744276133</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K28" t="n">
-        <v>1.37</v>
+        <v>0.78</v>
       </c>
       <c r="L28" t="n">
         <v>0.97</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.17</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H29" t="n">
-        <v>29114.25</v>
+        <v>29455.55</v>
       </c>
       <c r="I29" t="n">
         <v>29237.4355676717</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K29" t="n">
-        <v>5.2</v>
+        <v>4.09</v>
       </c>
       <c r="L29" t="n">
         <v>0.52</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.76</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43223</v>
+        <v>43224</v>
       </c>
       <c r="H30" t="n">
-        <v>29898.9</v>
+        <v>29703.95</v>
       </c>
       <c r="I30" t="n">
         <v>29847.20182676071</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>1.51</v>
+        <v>0.84</v>
       </c>
       <c r="L30" t="n">
         <v>1.29</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>3.6</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H31" t="n">
-        <v>29339.15</v>
+        <v>29548.75</v>
       </c>
       <c r="I31" t="n">
         <v>29466.18479997737</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K31" t="n">
-        <v>1.23</v>
+        <v>0.52</v>
       </c>
       <c r="L31" t="n">
         <v>1.08</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.89</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43273</v>
+        <v>43276</v>
       </c>
       <c r="H32" t="n">
-        <v>28829.45</v>
+        <v>28447.7</v>
       </c>
       <c r="I32" t="n">
         <v>28554.05537082224</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.43</v>
+        <v>-3.73</v>
       </c>
       <c r="L32" t="n">
-        <v>3.72</v>
+        <v>3.87</v>
       </c>
       <c r="M32" t="n">
         <v>0.21</v>
       </c>
       <c r="N32" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="O32" t="n">
         <v>0.71</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.27</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H33" t="n">
-        <v>28065.85</v>
+        <v>28786.25</v>
       </c>
       <c r="I33" t="n">
         <v>28621.96788310274</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>1.34</v>
+        <v>-1.19</v>
       </c>
       <c r="L33" t="n">
         <v>1.52</v>
@@ -2322,7 +2717,7 @@
         <v>0.6</v>
       </c>
       <c r="N33" t="n">
-        <v>1.87</v>
+        <v>2.57</v>
       </c>
       <c r="O33" t="n">
         <v>-1.32</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.52</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H34" t="n">
-        <v>31022.25</v>
+        <v>30074.85</v>
       </c>
       <c r="I34" t="n">
         <v>30318.09280748352</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K34" t="n">
-        <v>7.77</v>
+        <v>4.48</v>
       </c>
       <c r="L34" t="n">
         <v>2.21</v>
@@ -2379,7 +2786,7 @@
         <v>0.52</v>
       </c>
       <c r="N34" t="n">
-        <v>1.07</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
         <v>2.57</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.36</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43405</v>
+        <v>43406</v>
       </c>
       <c r="H35" t="n">
-        <v>26728.8</v>
+        <v>27134.9</v>
       </c>
       <c r="I35" t="n">
         <v>27049.40003659149</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K35" t="n">
-        <v>11.13</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>3.23</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.15</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H36" t="n">
-        <v>26915.65</v>
+        <v>26426.05</v>
       </c>
       <c r="I36" t="n">
         <v>26778.79458563203</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.61</v>
       </c>
       <c r="L36" t="n">
-        <v>1.51</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>0.63</v>
+        <v>1.64</v>
       </c>
       <c r="N36" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="O36" t="n">
         <v>1.52</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>4.01</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43446</v>
+        <v>43447</v>
       </c>
       <c r="H37" t="n">
-        <v>27440.85</v>
+        <v>27720.5</v>
       </c>
       <c r="I37" t="n">
         <v>27484.57525236683</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.84</v>
+        <v>-4.9</v>
       </c>
       <c r="L37" t="n">
-        <v>3.96</v>
+        <v>5.49</v>
       </c>
       <c r="M37" t="n">
         <v>0.46</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.58</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43483</v>
+        <v>43486</v>
       </c>
       <c r="H38" t="n">
-        <v>27410.55</v>
+        <v>27322.4</v>
       </c>
       <c r="I38" t="n">
         <v>27322.42239476561</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.12</v>
+        <v>-1.44</v>
       </c>
       <c r="L38" t="n">
         <v>2.1</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>3.84</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43523</v>
+        <v>43524</v>
       </c>
       <c r="H39" t="n">
-        <v>26310.85</v>
+        <v>26514.45</v>
       </c>
       <c r="I39" t="n">
         <v>26464.16357078423</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K39" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="L39" t="n">
         <v>1.08</v>
       </c>
       <c r="M39" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="N39" t="n">
         <v>1.34</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.29</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H40" t="n">
-        <v>27800.25</v>
+        <v>27659.1</v>
       </c>
       <c r="I40" t="n">
         <v>27761.83098281274</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K40" t="n">
-        <v>4.85</v>
+        <v>4.32</v>
       </c>
       <c r="L40" t="n">
         <v>0.63</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>3.4</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H41" t="n">
-        <v>26226.5</v>
+        <v>27081.4</v>
       </c>
       <c r="I41" t="n">
         <v>26883.53320831925</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>5.18</v>
+        <v>2.09</v>
       </c>
       <c r="L41" t="n">
         <v>0.86</v>
       </c>
       <c r="M41" t="n">
-        <v>0.34</v>
+        <v>2.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0.85</v>
+        <v>3.26</v>
       </c>
       <c r="O41" t="n">
         <v>-0.51</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>5.03</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H42" t="n">
-        <v>27093</v>
+        <v>26672.3</v>
       </c>
       <c r="I42" t="n">
         <v>27021.95529041293</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>0.04</v>
+        <v>-1.51</v>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="M42" t="n">
         <v>0.28</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>4.78</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>43649</v>
+        <v>43650</v>
       </c>
       <c r="H43" t="n">
-        <v>27704.9</v>
+        <v>27762</v>
       </c>
       <c r="I43" t="n">
         <v>27737.80099529029</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.87</v>
+        <v>-4.09</v>
       </c>
       <c r="L43" t="n">
-        <v>3.93</v>
+        <v>4.3</v>
       </c>
       <c r="M43" t="n">
         <v>0.39</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>2.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H44" t="n">
-        <v>27378</v>
+        <v>26810.65</v>
       </c>
       <c r="I44" t="n">
         <v>26991.7429354024</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.38</v>
+        <v>-3.43</v>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>3.79</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="N44" t="n">
-        <v>1.38</v>
+        <v>2.07</v>
       </c>
       <c r="O44" t="n">
         <v>0.21</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.25</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>43720</v>
+        <v>43721</v>
       </c>
       <c r="H45" t="n">
-        <v>26285</v>
+        <v>26460.1</v>
       </c>
       <c r="I45" t="n">
         <v>26422.8030843023</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K45" t="n">
-        <v>1.96</v>
+        <v>1.31</v>
       </c>
       <c r="L45" t="n">
         <v>2.75</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.67</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>43742</v>
+        <v>43745</v>
       </c>
       <c r="H46" t="n">
-        <v>26681.6</v>
+        <v>26295.05</v>
       </c>
       <c r="I46" t="n">
         <v>26415.80805197988</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>0.84</v>
+        <v>-0.62</v>
       </c>
       <c r="L46" t="n">
         <v>2.45</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>6.25</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>43755</v>
+        <v>43756</v>
       </c>
       <c r="H47" t="n">
-        <v>27627.6</v>
+        <v>28014.15</v>
       </c>
       <c r="I47" t="n">
         <v>27902.76762217276</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.07</v>
+        <v>-6.54</v>
       </c>
       <c r="L47" t="n">
-        <v>5.16</v>
+        <v>6.73</v>
       </c>
       <c r="M47" t="n">
         <v>0.3</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.06</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>43805</v>
+        <v>43808</v>
       </c>
       <c r="H48" t="n">
-        <v>27854.05</v>
+        <v>27758.05</v>
       </c>
       <c r="I48" t="n">
         <v>27762.35084504395</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.57</v>
+        <v>-0.91</v>
       </c>
       <c r="L48" t="n">
         <v>1.46</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>3.85</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>43826</v>
+        <v>43829</v>
       </c>
       <c r="H49" t="n">
-        <v>28476.8</v>
+        <v>28484.85</v>
       </c>
       <c r="I49" t="n">
         <v>28482.48709657829</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.59</v>
+        <v>-2.62</v>
       </c>
       <c r="L49" t="n">
-        <v>2.76</v>
+        <v>3.08</v>
       </c>
       <c r="M49" t="n">
         <v>0.51</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>2.44</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H50" t="n">
-        <v>28294.6</v>
+        <v>27340.5</v>
       </c>
       <c r="I50" t="n">
         <v>28217.82465490896</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.67</v>
+        <v>-4.02</v>
       </c>
       <c r="L50" t="n">
-        <v>2.62</v>
+        <v>4.46</v>
       </c>
       <c r="M50" t="n">
         <v>1.29</v>
       </c>
       <c r="N50" t="n">
-        <v>2.05</v>
+        <v>3.37</v>
       </c>
       <c r="O50" t="n">
         <v>0.03</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.98</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>43866</v>
+        <v>43867</v>
       </c>
       <c r="H51" t="n">
-        <v>28537.8</v>
+        <v>28871.35</v>
       </c>
       <c r="I51" t="n">
         <v>28774.43465598452</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.38</v>
+        <v>-5.6</v>
       </c>
       <c r="L51" t="n">
-        <v>4.67</v>
+        <v>5.83</v>
       </c>
       <c r="M51" t="n">
         <v>0.71</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.18</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H52" t="n">
-        <v>27863.65</v>
+        <v>27470.15</v>
       </c>
       <c r="I52" t="n">
         <v>27741.39833733893</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.49</v>
+        <v>-4.85</v>
       </c>
       <c r="L52" t="n">
-        <v>3.88</v>
+        <v>5.09</v>
       </c>
       <c r="M52" t="n">
         <v>0.67</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.33</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H53" t="n">
-        <v>22139.65</v>
+        <v>22898.85</v>
       </c>
       <c r="I53" t="n">
         <v>22815.57983989933</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K53" t="n">
-        <v>19.4</v>
+        <v>16.64</v>
       </c>
       <c r="L53" t="n">
         <v>1.3</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>14.74</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H54" t="n">
-        <v>28018.75</v>
+        <v>26824.15</v>
       </c>
       <c r="I54" t="n">
         <v>27188.05936997651</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K54" t="n">
-        <v>22.36</v>
+        <v>17.14</v>
       </c>
       <c r="L54" t="n">
         <v>2.33</v>
@@ -3519,7 +4166,7 @@
         <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
       <c r="O54" t="n">
         <v>3.43</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.94</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44105</v>
+        <v>44109</v>
       </c>
       <c r="H55" t="n">
-        <v>27250.95</v>
+        <v>27321.3</v>
       </c>
       <c r="I55" t="n">
         <v>27319.54092573862</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.59</v>
+        <v>-1.85</v>
       </c>
       <c r="L55" t="n">
         <v>5.06</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.93</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H56" t="n">
-        <v>32082.75</v>
+        <v>30971.5</v>
       </c>
       <c r="I56" t="n">
         <v>31037.29697891039</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K56" t="n">
-        <v>17.43</v>
+        <v>13.36</v>
       </c>
       <c r="L56" t="n">
         <v>1.71</v>
@@ -3633,7 +4304,7 @@
         <v>0.74</v>
       </c>
       <c r="N56" t="n">
-        <v>1.68</v>
+        <v>3.46</v>
       </c>
       <c r="O56" t="n">
         <v>0.26</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>5.63</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44196</v>
+        <v>44197</v>
       </c>
       <c r="H57" t="n">
-        <v>32508.55</v>
+        <v>32765.95</v>
       </c>
       <c r="I57" t="n">
         <v>32667.80167213689</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.96</v>
+        <v>-5.79</v>
       </c>
       <c r="L57" t="n">
-        <v>5.23</v>
+        <v>5.93</v>
       </c>
       <c r="M57" t="n">
         <v>0.85</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>4.58</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H58" t="n">
-        <v>33080.45</v>
+        <v>32642.55</v>
       </c>
       <c r="I58" t="n">
         <v>32969.47186683876</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K58" t="n">
-        <v>0.96</v>
+        <v>-0.38</v>
       </c>
       <c r="L58" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="M58" t="n">
         <v>0.19</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.28</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44236</v>
+        <v>44237</v>
       </c>
       <c r="H59" t="n">
-        <v>34147.3</v>
+        <v>34281.55</v>
       </c>
       <c r="I59" t="n">
         <v>34229.71112936563</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.61</v>
+        <v>-5.02</v>
       </c>
       <c r="L59" t="n">
         <v>5.45</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>5.7</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H60" t="n">
-        <v>34102.1</v>
+        <v>33692.85</v>
       </c>
       <c r="I60" t="n">
         <v>33935.40757020897</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.52</v>
+        <v>-1.72</v>
       </c>
       <c r="L60" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="M60" t="n">
         <v>1.06</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.23</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H61" t="n">
-        <v>35816.95</v>
+        <v>36190.15</v>
       </c>
       <c r="I61" t="n">
         <v>35877.10376163511</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.3</v>
+        <v>-7.41</v>
       </c>
       <c r="L61" t="n">
-        <v>6.69</v>
+        <v>7.51</v>
       </c>
       <c r="M61" t="n">
         <v>1.09</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.32</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H62" t="n">
-        <v>44085.45</v>
+        <v>43322.7</v>
       </c>
       <c r="I62" t="n">
         <v>43354.38603713937</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K62" t="n">
-        <v>21.82</v>
+        <v>19.71</v>
       </c>
       <c r="L62" t="n">
         <v>1.55</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>6</v>
+      </c>
+      <c r="U62" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>5.15</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>44512</v>
+        <v>44515</v>
       </c>
       <c r="H63" t="n">
-        <v>44242.55</v>
+        <v>44362.15</v>
       </c>
       <c r="I63" t="n">
         <v>44294.76885877604</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.12</v>
+        <v>-2.4</v>
       </c>
       <c r="L63" t="n">
-        <v>2.18</v>
+        <v>2.79</v>
       </c>
       <c r="M63" t="n">
         <v>0.75</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>3.86</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H64" t="n">
-        <v>43588.7</v>
+        <v>42271.35</v>
       </c>
       <c r="I64" t="n">
         <v>42737.25617612127</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.74</v>
+        <v>-4.71</v>
       </c>
       <c r="L64" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M64" t="n">
-        <v>0.37</v>
+        <v>0.92</v>
       </c>
       <c r="N64" t="n">
-        <v>1.86</v>
+        <v>3.02</v>
       </c>
       <c r="O64" t="n">
         <v>0.27</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.64</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H65" t="n">
-        <v>42556.35</v>
+        <v>42760.4</v>
       </c>
       <c r="I65" t="n">
         <v>42652.03376523779</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.67</v>
+        <v>-1.16</v>
       </c>
       <c r="L65" t="n">
         <v>2.7</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>4.35</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H66" t="n">
-        <v>42182.2</v>
+        <v>40616.05</v>
       </c>
       <c r="I66" t="n">
         <v>42177.637712137</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.35</v>
+        <v>-5.01</v>
       </c>
       <c r="L66" t="n">
-        <v>2.17</v>
+        <v>5.99</v>
       </c>
       <c r="M66" t="n">
         <v>0.54</v>
       </c>
       <c r="N66" t="n">
-        <v>1.73</v>
+        <v>3.71</v>
       </c>
       <c r="O66" t="n">
         <v>0.48</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.63</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H67" t="n">
-        <v>40462</v>
+        <v>41059</v>
       </c>
       <c r="I67" t="n">
         <v>40982.00473433587</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K67" t="n">
-        <v>0.38</v>
+        <v>-1.09</v>
       </c>
       <c r="L67" t="n">
         <v>4.11</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.41</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H68" t="n">
-        <v>42381.15</v>
+        <v>41162.35</v>
       </c>
       <c r="I68" t="n">
         <v>41876.54814184521</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K68" t="n">
-        <v>3.22</v>
+        <v>0.25</v>
       </c>
       <c r="L68" t="n">
         <v>2.65</v>
@@ -4317,7 +5132,7 @@
         <v>1.02</v>
       </c>
       <c r="N68" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="O68" t="n">
         <v>1.48</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.5</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H69" t="n">
-        <v>37306</v>
+        <v>37937.65</v>
       </c>
       <c r="I69" t="n">
         <v>37711.94791745579</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K69" t="n">
-        <v>9.369999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="L69" t="n">
         <v>3.44</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.98</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H70" t="n">
-        <v>44207.2</v>
+        <v>43415.05</v>
       </c>
       <c r="I70" t="n">
         <v>43574.54520571412</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K70" t="n">
-        <v>16.53</v>
+        <v>14.44</v>
       </c>
       <c r="L70" t="n">
         <v>1.89</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.22</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>44894</v>
+        <v>44895</v>
       </c>
       <c r="H71" t="n">
-        <v>43147.1</v>
+        <v>43687.9</v>
       </c>
       <c r="I71" t="n">
         <v>43655.1222342203</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K71" t="n">
-        <v>0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="L71" t="n">
         <v>2.2</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>3.2</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H72" t="n">
-        <v>43329.25</v>
+        <v>42638.65</v>
       </c>
       <c r="I72" t="n">
         <v>42958.06858993554</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.82</v>
+        <v>-2.4</v>
       </c>
       <c r="L72" t="n">
-        <v>1.92</v>
+        <v>2.74</v>
       </c>
       <c r="M72" t="n">
         <v>0.34</v>
       </c>
       <c r="N72" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="O72" t="n">
         <v>1.25</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.6</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H73" t="n">
-        <v>38379.65</v>
+        <v>38560.9</v>
       </c>
       <c r="I73" t="n">
         <v>38419.69345869037</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K73" t="n">
-        <v>9.99</v>
+        <v>9.56</v>
       </c>
       <c r="L73" t="n">
         <v>2.3</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>5</v>
+      </c>
+      <c r="U73" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>2.99</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H74" t="n">
-        <v>43387.15</v>
+        <v>42833.15</v>
       </c>
       <c r="I74" t="n">
         <v>42921.33341227366</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K74" t="n">
-        <v>12.52</v>
+        <v>11.08</v>
       </c>
       <c r="L74" t="n">
         <v>0.67</v>
@@ -4659,7 +5546,7 @@
         <v>0.11</v>
       </c>
       <c r="N74" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="O74" t="n">
         <v>0.47</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>3.44</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45111</v>
+        <v>45112</v>
       </c>
       <c r="H75" t="n">
-        <v>43758.2</v>
+        <v>44108</v>
       </c>
       <c r="I75" t="n">
         <v>44061.0560174525</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.16</v>
+        <v>-2.98</v>
       </c>
       <c r="L75" t="n">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="M75" t="n">
         <v>0.44</v>
       </c>
       <c r="N75" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="O75" t="n">
         <v>-1.28</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>2.76</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
       <c r="H76" t="n">
-        <v>44566.7</v>
+        <v>44008.75</v>
       </c>
       <c r="I76" t="n">
         <v>44312.60308380365</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K76" t="n">
-        <v>1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="L76" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="M76" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="N76" t="n">
         <v>1.36</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>3.06</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45170</v>
+        <v>45173</v>
       </c>
       <c r="H77" t="n">
-        <v>44799.75</v>
+        <v>45201</v>
       </c>
       <c r="I77" t="n">
         <v>44969.98946793163</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K77" t="n">
-        <v>-1.8</v>
+        <v>-2.71</v>
       </c>
       <c r="L77" t="n">
-        <v>2.04</v>
+        <v>2.81</v>
       </c>
       <c r="M77" t="n">
         <v>0.63</v>
       </c>
       <c r="N77" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="O77" t="n">
         <v>-1.25</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>2.98</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H78" t="n">
-        <v>45620.65</v>
+        <v>45231.2</v>
       </c>
       <c r="I78" t="n">
         <v>45300.26995492341</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K78" t="n">
-        <v>0.93</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L78" t="n">
         <v>0.89</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>3.54</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H79" t="n">
-        <v>44451.1</v>
+        <v>44885</v>
       </c>
       <c r="I79" t="n">
         <v>44602.57751108995</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K79" t="n">
-        <v>1.72</v>
+        <v>0.77</v>
       </c>
       <c r="L79" t="n">
         <v>1.08</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>4.05</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H80" t="n">
-        <v>59377.2</v>
+        <v>57149.55</v>
       </c>
       <c r="I80" t="n">
         <v>58275.21644035129</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K80" t="n">
-        <v>32.29</v>
+        <v>27.32</v>
       </c>
       <c r="L80" t="n">
         <v>0.61</v>
@@ -5001,7 +5960,7 @@
         <v>0.9</v>
       </c>
       <c r="N80" t="n">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="O80" t="n">
         <v>0.98</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>5</v>
+      </c>
+      <c r="U80" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>7.14</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45378</v>
+        <v>45379</v>
       </c>
       <c r="H81" t="n">
-        <v>59911.7</v>
+        <v>60624.3</v>
       </c>
       <c r="I81" t="n">
         <v>60607.73368686094</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K81" t="n">
-        <v>-4.83</v>
+        <v>-6.08</v>
       </c>
       <c r="L81" t="n">
-        <v>5.6</v>
+        <v>6.46</v>
       </c>
       <c r="M81" t="n">
         <v>0.92</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>5.35</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H82" t="n">
-        <v>70620.25</v>
+        <v>64022.15</v>
       </c>
       <c r="I82" t="n">
         <v>66532.74541527891</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K82" t="n">
-        <v>16.49</v>
+        <v>5.6</v>
       </c>
       <c r="L82" t="n">
         <v>0.99</v>
@@ -5115,7 +6098,7 @@
         <v>1.57</v>
       </c>
       <c r="N82" t="n">
-        <v>2.12</v>
+        <v>9.34</v>
       </c>
       <c r="O82" t="n">
         <v>1.19</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5151,22 +6146,22 @@
         <v>12.24</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H83" t="n">
-        <v>70842.55</v>
+        <v>71892.14999999999</v>
       </c>
       <c r="I83" t="n">
         <v>71858.98162624898</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K83" t="n">
-        <v>-10.65</v>
+        <v>-12.29</v>
       </c>
       <c r="L83" t="n">
-        <v>10.8</v>
+        <v>12.41</v>
       </c>
       <c r="M83" t="n">
         <v>1.94</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>7.29</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H84" t="n">
-        <v>73112.5</v>
+        <v>71353</v>
       </c>
       <c r="I84" t="n">
         <v>71443.01763505947</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K84" t="n">
-        <v>1.7</v>
+        <v>-0.75</v>
       </c>
       <c r="L84" t="n">
         <v>2.1</v>
@@ -5229,7 +6236,7 @@
         <v>0.23</v>
       </c>
       <c r="N84" t="n">
-        <v>1.12</v>
+        <v>2.41</v>
       </c>
       <c r="O84" t="n">
         <v>1.48</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>5.6</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>45531</v>
+        <v>45532</v>
       </c>
       <c r="H85" t="n">
-        <v>74848.95</v>
+        <v>75082.55</v>
       </c>
       <c r="I85" t="n">
         <v>74894.03999404165</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K85" t="n">
-        <v>-4.9</v>
+        <v>-5.23</v>
       </c>
       <c r="L85" t="n">
-        <v>5.19</v>
+        <v>5.54</v>
       </c>
       <c r="M85" t="n">
         <v>1.84</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>3.39</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H86" t="n">
-        <v>75448.3</v>
+        <v>74620.25</v>
       </c>
       <c r="I86" t="n">
         <v>74822.95224426262</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K86" t="n">
-        <v>0.49</v>
+        <v>-0.62</v>
       </c>
       <c r="L86" t="n">
         <v>2.32</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>4.64</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H87" t="n">
-        <v>70726.85000000001</v>
+        <v>71164.35000000001</v>
       </c>
       <c r="I87" t="n">
         <v>70810.63361978841</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K87" t="n">
-        <v>5.22</v>
+        <v>4.63</v>
       </c>
       <c r="L87" t="n">
         <v>1.97</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>3</v>
+      </c>
+      <c r="U87" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -5436,25 +6491,25 @@
         <v>5.2</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H88" t="n">
-        <v>71250</v>
+        <v>70625.7</v>
       </c>
       <c r="I88" t="n">
         <v>70833.76722057311</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.12</v>
+        <v>-0.76</v>
       </c>
       <c r="L88" t="n">
-        <v>0.83</v>
+        <v>1.85</v>
       </c>
       <c r="M88" t="n">
-        <v>0.2</v>
+        <v>1.72</v>
       </c>
       <c r="N88" t="n">
         <v>1.32</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S88" t="b">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5493,19 +6560,19 @@
         <v>3.58</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H89" t="n">
-        <v>60971.4</v>
+        <v>61953.45</v>
       </c>
       <c r="I89" t="n">
         <v>60984.21979241831</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K89" t="n">
-        <v>13.67</v>
+        <v>12.28</v>
       </c>
       <c r="L89" t="n">
         <v>0.47</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>4</v>
+      </c>
+      <c r="U89" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -5550,28 +6629,28 @@
         <v>6.54</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H90" t="n">
-        <v>61468.7</v>
+        <v>59546.2</v>
       </c>
       <c r="I90" t="n">
         <v>60086.4577719839</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.78</v>
+        <v>-3.89</v>
       </c>
       <c r="L90" t="n">
-        <v>1.56</v>
+        <v>7.59</v>
       </c>
       <c r="M90" t="n">
-        <v>0.77</v>
+        <v>6.85</v>
       </c>
       <c r="N90" t="n">
-        <v>2.59</v>
+        <v>3.13</v>
       </c>
       <c r="O90" t="n">
         <v>1.61</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5607,28 +6698,28 @@
         <v>5.93</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H91" t="n">
-        <v>61473.55</v>
+        <v>63374.3</v>
       </c>
       <c r="I91" t="n">
         <v>63075.24838889267</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K91" t="n">
-        <v>-3.24</v>
+        <v>-6.43</v>
       </c>
       <c r="L91" t="n">
-        <v>3.85</v>
+        <v>6.56</v>
       </c>
       <c r="M91" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="N91" t="n">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O91" t="n">
         <v>-3.13</v>
@@ -5637,7 +6728,19 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5664,19 +6767,19 @@
         <v>7.78</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H92" t="n">
-        <v>66788.7</v>
+        <v>65848.14999999999</v>
       </c>
       <c r="I92" t="n">
         <v>66611.65996388324</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K92" t="n">
-        <v>5.39</v>
+        <v>3.9</v>
       </c>
       <c r="L92" t="n">
         <v>3.11</v>
@@ -5694,7 +6797,19 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>3</v>
+      </c>
+      <c r="U92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -5721,19 +6836,19 @@
         <v>4.93</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H93" t="n">
-        <v>67974.7</v>
+        <v>68194</v>
       </c>
       <c r="I93" t="n">
         <v>68146.07107439799</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K93" t="n">
-        <v>-3.23</v>
+        <v>-3.56</v>
       </c>
       <c r="L93" t="n">
         <v>5.06</v>
@@ -5751,7 +6866,19 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>4</v>
+      </c>
+      <c r="U93" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -5778,19 +6905,19 @@
         <v>2.85</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H94" t="n">
-        <v>68808.2</v>
+        <v>68293.64999999999</v>
       </c>
       <c r="I94" t="n">
         <v>68371.54269213918</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K94" t="n">
-        <v>0.9</v>
+        <v>0.15</v>
       </c>
       <c r="L94" t="n">
         <v>0.19</v>
@@ -5808,7 +6935,19 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S94" t="b">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5835,28 +6974,28 @@
         <v>3.48</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H95" t="n">
-        <v>69258.25</v>
+        <v>70238.45</v>
       </c>
       <c r="I95" t="n">
         <v>69748.12675696875</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K95" t="n">
-        <v>-1.41</v>
+        <v>-2.85</v>
       </c>
       <c r="L95" t="n">
-        <v>2.42</v>
+        <v>2.97</v>
       </c>
       <c r="M95" t="n">
         <v>0.51</v>
       </c>
       <c r="N95" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="O95" t="n">
         <v>-0.75</v>
@@ -5865,7 +7004,19 @@
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R95" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S95" t="b">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
+        <v>3</v>
+      </c>
+      <c r="U95" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -5892,22 +7043,22 @@
         <v>3.22</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H96" t="n">
-        <v>68669.14999999999</v>
+        <v>67997.45</v>
       </c>
       <c r="I96" t="n">
         <v>68519.18245374152</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K96" t="n">
-        <v>-2.23</v>
+        <v>-3.19</v>
       </c>
       <c r="L96" t="n">
-        <v>2.62</v>
+        <v>3.29</v>
       </c>
       <c r="M96" t="n">
         <v>0.32</v>
@@ -5922,7 +7073,19 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R96" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S96" t="b">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5949,22 +7112,22 @@
         <v>3.33</v>
       </c>
       <c r="G97" s="1" t="n">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="H97" t="n">
-        <v>69364.5</v>
+        <v>69675.39999999999</v>
       </c>
       <c r="I97" t="n">
         <v>69435.13088632592</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K97" t="n">
-        <v>-2.01</v>
+        <v>-2.47</v>
       </c>
       <c r="L97" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="M97" t="n">
         <v>0.38</v>
@@ -5979,7 +7142,19 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S97" t="b">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
+        <v>3</v>
+      </c>
+      <c r="U97" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -6006,25 +7181,25 @@
         <v>2.94</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H98" t="n">
-        <v>69196.10000000001</v>
+        <v>68492.2</v>
       </c>
       <c r="I98" t="n">
         <v>68854.91991068654</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.7</v>
       </c>
       <c r="L98" t="n">
-        <v>0.86</v>
+        <v>2.03</v>
       </c>
       <c r="M98" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="N98" t="n">
         <v>2.11</v>
@@ -6036,7 +7211,19 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S98" t="b">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6063,19 +7250,19 @@
         <v>3.87</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H99" t="n">
-        <v>69058.39999999999</v>
+        <v>69729.35000000001</v>
       </c>
       <c r="I99" t="n">
         <v>69485.44597460379</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.83</v>
+        <v>-1.81</v>
       </c>
       <c r="L99" t="n">
         <v>2.03</v>
@@ -6093,7 +7280,19 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S99" t="b">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
+        <v>2</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -6120,28 +7319,28 @@
         <v>5.74</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H100" t="n">
-        <v>68650.25</v>
+        <v>66799.39999999999</v>
       </c>
       <c r="I100" t="n">
         <v>67642.96468687103</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K100" t="n">
-        <v>-1.55</v>
+        <v>-4.2</v>
       </c>
       <c r="L100" t="n">
-        <v>3.41</v>
+        <v>4.66</v>
       </c>
       <c r="M100" t="n">
         <v>3.32</v>
       </c>
       <c r="N100" t="n">
-        <v>1.86</v>
+        <v>2.7</v>
       </c>
       <c r="O100" t="n">
         <v>0.97</v>
@@ -6150,7 +7349,19 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R100" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S100" t="b">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
+        <v>2</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -6177,28 +7388,28 @@
         <v>5.68</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H101" t="n">
-        <v>63151.05</v>
+        <v>66145.3</v>
       </c>
       <c r="I101" t="n">
         <v>65716.91309115577</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K101" t="n">
-        <v>5.46</v>
+        <v>0.98</v>
       </c>
       <c r="L101" t="n">
         <v>1.91</v>
       </c>
       <c r="M101" t="n">
-        <v>2.93</v>
+        <v>3.71</v>
       </c>
       <c r="N101" t="n">
-        <v>2.59</v>
+        <v>4.74</v>
       </c>
       <c r="O101" t="n">
         <v>-2.7</v>
@@ -6207,7 +7418,19 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R101" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S101" t="b">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>2</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6234,19 +7457,19 @@
         <v>8.49</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H102" t="n">
-        <v>69154.7</v>
+        <v>68378.75</v>
       </c>
       <c r="I102" t="n">
         <v>68551.52900595084</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K102" t="n">
-        <v>4.55</v>
+        <v>3.38</v>
       </c>
       <c r="L102" t="n">
         <v>1.29</v>
@@ -6264,7 +7487,19 @@
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R102" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S102" t="b">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
+        <v>3</v>
+      </c>
+      <c r="U102" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -6291,19 +7526,19 @@
         <v>5.12</v>
       </c>
       <c r="G103" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H103" t="n">
-        <v>71798.64999999999</v>
+        <v>72258.5</v>
       </c>
       <c r="I103" t="n">
         <v>71881.18900051253</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K103" t="n">
-        <v>-5</v>
+        <v>-5.67</v>
       </c>
       <c r="L103" t="n">
         <v>6.9</v>
@@ -6321,7 +7556,19 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R103" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S103" t="b">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6348,19 +7595,19 @@
         <v>5.4</v>
       </c>
       <c r="G104" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H104" t="n">
-        <v>73759.7</v>
+        <v>72874.75</v>
       </c>
       <c r="I104" t="n">
         <v>73108.77471585461</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K104" t="n">
-        <v>2.08</v>
+        <v>0.85</v>
       </c>
       <c r="L104" t="n">
         <v>2.3</v>
@@ -6378,7 +7625,19 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R104" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S104" t="b">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
+        <v>4</v>
+      </c>
+      <c r="U104" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -6429,6 +7688,14 @@
       <c r="Q105" t="n">
         <v>39</v>
       </c>
+      <c r="R105" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S105" t="b">
+        <v>1</v>
+      </c>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11387,7 +12654,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.6</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="6">
@@ -11397,7 +12664,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -11407,7 +12674,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8">
@@ -11417,7 +12684,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -11427,7 +12694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="10">
@@ -11437,7 +12704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74.8</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="11">
@@ -11447,7 +12714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -11457,7 +12724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -11467,7 +12734,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="14">
@@ -11477,7 +12744,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.11</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="15">
@@ -11487,7 +12754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="16">
@@ -11497,7 +12764,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="17">
@@ -11507,7 +12774,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.29</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="18">
@@ -11517,7 +12784,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.5</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="19">
@@ -11527,7 +12794,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.58</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="20">
@@ -11537,7 +12804,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.21</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="21">
@@ -11547,7 +12814,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.8</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="22">
@@ -11557,7 +12824,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -11577,7 +12844,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.97</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="25">
@@ -11587,7 +12854,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.6</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="26">
@@ -11597,7 +12864,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="27">
@@ -11607,7 +12874,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.39</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="28">
@@ -11617,7 +12884,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
